--- a/GATEWAY/A1#111#ITLAB/ITLAB_SRL/QuickClinica/v1.25.0.90/accreditamento-checklist_V9.0.0_ITLAB.xlsx
+++ b/GATEWAY/A1#111#ITLAB/ITLAB_SRL/QuickClinica/v1.25.0.90/accreditamento-checklist_V9.0.0_ITLAB.xlsx
@@ -237,7 +237,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>v2.0.0.1</t>
+      <t>v1.25.0.90</t>
     </r>
   </si>
   <si>
